--- a/finance_data_log.xlsx
+++ b/finance_data_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,23 @@
       <c r="C2" t="inlineStr">
         <is>
           <t>6,475.81</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-04-24 06:30:52</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1,483.80</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6,481.33</t>
         </is>
       </c>
     </row>

--- a/finance_data_log.xlsx
+++ b/finance_data_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,6 +476,23 @@
       <c r="C3" t="inlineStr">
         <is>
           <t>6,481.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-04-25 06:07:38</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1,477.50</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>6,475.63</t>
         </is>
       </c>
     </row>

--- a/finance_data_log.xlsx
+++ b/finance_data_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,6 +491,23 @@
         </is>
       </c>
       <c r="C4" t="inlineStr">
+        <is>
+          <t>6,475.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-26 06:31:25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1,477.50</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>6,475.63</t>
         </is>

--- a/finance_data_log.xlsx
+++ b/finance_data_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,6 +510,23 @@
       <c r="C5" t="inlineStr">
         <is>
           <t>6,475.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-27 07:59:05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1,470.80</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6,615.03</t>
         </is>
       </c>
     </row>

--- a/finance_data_log.xlsx
+++ b/finance_data_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -530,6 +530,23 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-28 07:57:54</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1,474.00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6,641.02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finance_data_log.xlsx
+++ b/finance_data_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,6 +547,23 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-29 07:52:37</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1,478.60</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6,690.90</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finance_data_log.xlsx
+++ b/finance_data_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -564,6 +564,23 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-30 07:54:48</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1,482.10</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>6,598.87</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finance_data_log.xlsx
+++ b/finance_data_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -581,6 +581,23 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-01 07:54:10</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1,475.50</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>6,598.87</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finance_data_log.xlsx
+++ b/finance_data_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -598,6 +598,23 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-02 06:31:45</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1,475.00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>6,598.87</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finance_data_log.xlsx
+++ b/finance_data_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,6 +615,23 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-03 07:31:09</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1,477.00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>6,598.87</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finance_data_log.xlsx
+++ b/finance_data_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -632,6 +632,23 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-04 09:07:03</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1,469.30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>6,936.99</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finance_data_log.xlsx
+++ b/finance_data_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -649,6 +649,23 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-05 07:33:27</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1,474.60</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>6,936.99</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finance_data_log.xlsx
+++ b/finance_data_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -666,6 +666,23 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-07 09:45:34</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1,451.70</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>7,490.05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finance_data_log.xlsx
+++ b/finance_data_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,6 +683,23 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-08 06:19:13</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1,468.70</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>7,508.20</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finance_data_log.xlsx
+++ b/finance_data_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -700,6 +700,23 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-09 07:23:31</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1,465.50</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>7,498.00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finance_data_log.xlsx
+++ b/finance_data_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,6 +717,23 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-10 07:49:46</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1,465.50</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>7,498.00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finance_data_log.xlsx
+++ b/finance_data_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,6 +734,23 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-11 11:48:19</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1,472.00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>7,822.24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/finance_data_log.xlsx
+++ b/finance_data_log.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -751,6 +751,23 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-12 10:03:25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1,490.10</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>7,643.15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
